--- a/data/trans_orig/IQ19A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ19A-Estudios-trans_orig.xlsx
@@ -958,7 +958,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>3890</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>3682</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>3603</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>3199</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>4769</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>591</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5414</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1634,12 +1634,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3249</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>631</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6015</t>
+          <t>5830</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>3608</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>5091</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>601</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>634</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6484</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1967,12 +1967,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>681</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6298</t>
+          <t>6403</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2037,12 +2037,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -2063,12 +2063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7674</t>
+          <t>7133</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2098,12 +2098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>593</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>10183</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,32%</t>
         </is>
       </c>
     </row>
@@ -2174,12 +2174,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12455</t>
+          <t>12633</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20856</t>
+          <t>20993</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2209,12 +2209,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13872</t>
+          <t>14024</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19482</t>
+          <t>19477</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28887</t>
+          <t>28997</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39132</t>
+          <t>39487</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>78,8%</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>2718</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2837</t>
+          <t>3558</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3331</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3456</t>
+          <t>3438</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3895</t>
+          <t>3486</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -3290,12 +3290,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8418</t>
+          <t>8049</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>19877</t>
+          <t>19175</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>9095</t>
+          <t>9304</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>20734</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3340,12 +3340,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>20260</t>
+          <t>20588</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>35861</t>
+          <t>37543</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3375,12 +3375,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4479</t>
+          <t>4439</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -3512,12 +3512,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3590</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11806</t>
+          <t>12120</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5268</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>14688</t>
+          <t>15425</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -3623,12 +3623,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11269</t>
+          <t>11905</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>8458</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3693,12 +3693,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5773</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>16705</t>
+          <t>15918</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3708,12 +3708,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -3734,12 +3734,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>9340</t>
+          <t>8817</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>20608</t>
+          <t>20940</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>13027</t>
+          <t>13042</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>26212</t>
+          <t>26025</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>25535</t>
+          <t>24814</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>43179</t>
+          <t>41587</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -3845,12 +3845,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>90524</t>
+          <t>89343</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>107617</t>
+          <t>107130</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>97310</t>
+          <t>97081</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>114704</t>
+          <t>114472</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>191752</t>
+          <t>193697</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>216984</t>
+          <t>216897</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,97%</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4345</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -4961,12 +4961,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>8410</t>
+          <t>8026</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -4976,12 +4976,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -4996,12 +4996,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2149</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>9320</t>
+          <t>8980</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>5557</t>
+          <t>5143</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>15017</t>
+          <t>14818</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5046,12 +5046,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>723</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>6107</t>
+          <t>6118</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2918</t>
+          <t>3721</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>795</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6916</t>
+          <t>7835</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3535</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>523</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -5405,12 +5405,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>3973</t>
+          <t>3778</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>12434</t>
+          <t>12747</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5420,12 +5420,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>1452</t>
+          <t>1614</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>8411</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5455,12 +5455,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>17692</t>
+          <t>18014</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5490,12 +5490,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,6%</t>
         </is>
       </c>
     </row>
@@ -5516,12 +5516,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>28190</t>
+          <t>28585</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>39022</t>
+          <t>39210</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5531,12 +5531,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5551,12 +5551,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>26342</t>
+          <t>26994</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>35554</t>
+          <t>35553</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5586,12 +5586,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>58055</t>
+          <t>58375</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>71743</t>
+          <t>72502</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5601,12 +5601,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>78,88%</t>
         </is>
       </c>
     </row>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3756</t>
+          <t>3954</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>4048</t>
+          <t>3621</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>4719</t>
+          <t>3832</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3553</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>5577</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>4125</t>
+          <t>3333</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>3581</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3232</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3316</t>
+          <t>3193</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -6632,12 +6632,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>13049</t>
+          <t>13092</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>26864</t>
+          <t>27021</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6647,12 +6647,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6667,12 +6667,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>13898</t>
+          <t>13651</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>27879</t>
+          <t>27653</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>31109</t>
+          <t>30074</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>50594</t>
+          <t>49709</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>4341</t>
+          <t>5082</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>627</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>6637</t>
+          <t>6520</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>17298</t>
+          <t>17057</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>839</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>7413</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -6904,12 +6904,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>9351</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>21976</t>
+          <t>21498</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -6939,12 +6939,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -6965,12 +6965,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>5996</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>16503</t>
+          <t>16107</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7000,12 +7000,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>8857</t>
+          <t>8989</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>9660</t>
+          <t>9627</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>22599</t>
+          <t>22127</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -7076,12 +7076,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>18207</t>
+          <t>18784</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>34081</t>
+          <t>34436</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7091,12 +7091,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7111,12 +7111,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>17738</t>
+          <t>16724</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>33650</t>
+          <t>33067</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>40407</t>
+          <t>40008</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>62895</t>
+          <t>61289</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -7187,12 +7187,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>138973</t>
+          <t>137678</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>161586</t>
+          <t>160312</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7202,12 +7202,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>144634</t>
+          <t>144746</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>166579</t>
+          <t>165683</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7237,12 +7237,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7257,12 +7257,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>288920</t>
+          <t>290395</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>321299</t>
+          <t>319744</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,13%</t>
         </is>
       </c>
     </row>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2514</t>
+          <t>3204</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8513,7 +8513,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>2738</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4652</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -8650,7 +8650,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2268</t>
+          <t>2643</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8665,7 +8665,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4660</t>
+          <t>5358</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6955</t>
+          <t>6612</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,22%</t>
         </is>
       </c>
     </row>
@@ -8796,7 +8796,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>2953</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3754</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3776</t>
+          <t>4413</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8887,7 +8887,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8907,7 +8907,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3310</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8922,7 +8922,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5396</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8957,7 +8957,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -8978,12 +8978,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9057</t>
+          <t>7853</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9013,12 +9013,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4901</t>
+          <t>4860</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13425</t>
+          <t>13409</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9048,12 +9048,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8617</t>
+          <t>8468</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18583</t>
+          <t>18591</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9063,12 +9063,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,35%</t>
         </is>
       </c>
     </row>
@@ -9089,12 +9089,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13638</t>
+          <t>14523</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21219</t>
+          <t>21476</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9104,12 +9104,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9124,12 +9124,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11843</t>
+          <t>11578</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20733</t>
+          <t>20899</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9139,12 +9139,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9159,12 +9159,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28619</t>
+          <t>28663</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40104</t>
+          <t>40065</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9174,12 +9174,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>74,02%</t>
         </is>
       </c>
     </row>
@@ -9877,7 +9877,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9892,7 +9892,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -10205,12 +10205,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5886</t>
+          <t>5911</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>15945</t>
+          <t>16534</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3668</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>11192</t>
+          <t>11583</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10255,12 +10255,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>11228</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>24119</t>
+          <t>23430</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10290,12 +10290,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -10321,7 +10321,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3065</t>
+          <t>3384</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10351,12 +10351,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>564</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6166</t>
+          <t>6224</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,7 +10371,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10386,12 +10386,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>689</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7068</t>
+          <t>6581</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10401,12 +10401,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -10432,7 +10432,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3796</t>
+          <t>4498</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10462,12 +10462,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10477,12 +10477,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10497,12 +10497,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1353</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8290</t>
+          <t>8653</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10512,12 +10512,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -10538,12 +10538,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5706</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>15867</t>
+          <t>15688</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10573,12 +10573,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>10289</t>
+          <t>10048</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10608,12 +10608,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>9168</t>
+          <t>9846</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>21962</t>
+          <t>21830</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10623,12 +10623,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -10649,12 +10649,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>17117</t>
+          <t>18017</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>32950</t>
+          <t>32977</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10664,12 +10664,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10684,12 +10684,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>11419</t>
+          <t>11259</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>24917</t>
+          <t>23759</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10699,12 +10699,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10719,12 +10719,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>31926</t>
+          <t>31986</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>51048</t>
+          <t>52102</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,4%</t>
         </is>
       </c>
     </row>
@@ -10760,12 +10760,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>80764</t>
+          <t>80180</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>100115</t>
+          <t>98964</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10775,12 +10775,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>88907</t>
+          <t>89018</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>105712</t>
+          <t>104714</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>175457</t>
+          <t>176783</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>200079</t>
+          <t>200926</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10845,12 +10845,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,82%</t>
         </is>
       </c>
     </row>
@@ -11139,7 +11139,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3522</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -11154,7 +11154,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>4032</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -11326,7 +11326,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>3874</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -11361,7 +11361,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2575</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -11376,7 +11376,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -11396,7 +11396,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4128</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -11659,7 +11659,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11674,7 +11674,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11729,7 +11729,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>4818</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -11876,12 +11876,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>725</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>7191</t>
+          <t>7547</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>9304</t>
+          <t>9583</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11946,12 +11946,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>4646</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>14387</t>
+          <t>13708</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11961,12 +11961,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -11992,7 +11992,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2239</t>
+          <t>2251</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -12007,7 +12007,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -12027,7 +12027,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>5775</t>
+          <t>5671</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>452</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>5785</t>
+          <t>6545</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -12077,7 +12077,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -12103,7 +12103,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>3098</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -12138,7 +12138,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2519</t>
+          <t>2282</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -12153,7 +12153,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>3407</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -12188,7 +12188,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -12209,12 +12209,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -12224,12 +12224,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -12279,12 +12279,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>1498</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>8359</t>
+          <t>8889</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -12294,12 +12294,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -12320,12 +12320,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>4126</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>12272</t>
+          <t>12479</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -12335,12 +12335,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -12355,12 +12355,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6104</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>16526</t>
+          <t>16413</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -12370,12 +12370,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>11686</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>24859</t>
+          <t>24789</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -12405,12 +12405,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -12431,12 +12431,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>32016</t>
+          <t>32918</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>43646</t>
+          <t>43385</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12446,12 +12446,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>27903</t>
+          <t>28120</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>39827</t>
+          <t>40588</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>64683</t>
+          <t>64096</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>80152</t>
+          <t>79736</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>72,87%</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>4844</t>
+          <t>4809</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12845,7 +12845,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>4032</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12860,7 +12860,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -12997,7 +12997,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>3555</t>
+          <t>4136</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -13012,7 +13012,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -13067,7 +13067,7 @@
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -13082,7 +13082,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -13219,7 +13219,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>4803</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -13234,7 +13234,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -13289,7 +13289,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>4764</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -13330,7 +13330,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>4223</t>
+          <t>4881</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -13345,7 +13345,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -13415,7 +13415,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -13476,7 +13476,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>3679</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13511,7 +13511,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -13547,12 +13547,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>8728</t>
+          <t>8493</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>20689</t>
+          <t>20430</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -13562,12 +13562,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -13582,12 +13582,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>8327</t>
+          <t>7727</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>19284</t>
+          <t>19168</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -13597,12 +13597,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -13617,12 +13617,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>18980</t>
+          <t>19006</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>35560</t>
+          <t>35795</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -13632,12 +13632,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -13658,12 +13658,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>440</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -13678,7 +13678,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -13693,12 +13693,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>10512</t>
+          <t>10673</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -13708,12 +13708,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -13728,12 +13728,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>12104</t>
+          <t>12701</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -13743,12 +13743,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -13774,7 +13774,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>4674</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -13789,7 +13789,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -13804,12 +13804,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>8942</t>
+          <t>8887</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -13824,7 +13824,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -13839,12 +13839,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>2924</t>
+          <t>2559</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>11217</t>
+          <t>9931</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -13854,12 +13854,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -13880,12 +13880,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>10144</t>
+          <t>9855</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>21833</t>
+          <t>22292</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -13915,12 +13915,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>10857</t>
+          <t>10972</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -13950,12 +13950,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>14976</t>
+          <t>14936</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>30325</t>
+          <t>29181</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -13965,12 +13965,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -13991,12 +13991,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>27267</t>
+          <t>27144</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>44829</t>
+          <t>45234</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -14006,12 +14006,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -14026,12 +14026,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>27776</t>
+          <t>28341</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>45989</t>
+          <t>45122</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -14041,12 +14041,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -14061,12 +14061,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>60109</t>
+          <t>58887</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>86427</t>
+          <t>84994</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -14076,12 +14076,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -14102,12 +14102,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>134960</t>
+          <t>136364</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>157006</t>
+          <t>157964</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -14117,12 +14117,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -14137,12 +14137,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>137295</t>
+          <t>137334</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>158835</t>
+          <t>159036</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -14152,12 +14152,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>278761</t>
+          <t>279017</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>310860</t>
+          <t>310932</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -14187,12 +14187,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,96%</t>
         </is>
       </c>
     </row>
@@ -15489,7 +15489,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>2721</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -15524,7 +15524,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3421</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -15539,7 +15539,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -15711,7 +15711,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2948</t>
+          <t>2905</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -15746,7 +15746,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -15761,7 +15761,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -15787,7 +15787,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5095</t>
+          <t>4472</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -15802,7 +15802,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -15857,7 +15857,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>4587</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -15872,7 +15872,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -15898,7 +15898,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15913,7 +15913,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15928,12 +15928,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>557</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5487</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15943,12 +15943,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15963,12 +15963,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7131</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15978,12 +15978,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,38%</t>
         </is>
       </c>
     </row>
@@ -16004,12 +16004,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>4571</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9626</t>
+          <t>9630</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -16019,12 +16019,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -16039,12 +16039,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6311</t>
+          <t>6613</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11384</t>
+          <t>11499</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -16054,12 +16054,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -16074,12 +16074,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12977</t>
+          <t>12871</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20256</t>
+          <t>20047</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -16089,12 +16089,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>86,72%</t>
         </is>
       </c>
     </row>
@@ -16570,7 +16570,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3801</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -16585,7 +16585,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -16640,7 +16640,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -16655,7 +16655,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -16681,7 +16681,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -16696,7 +16696,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -16751,7 +16751,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -16766,7 +16766,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -17014,7 +17014,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>2849</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -17029,7 +17029,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -17084,7 +17084,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -17099,7 +17099,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -17120,12 +17120,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>5568</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>15448</t>
+          <t>15164</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -17135,12 +17135,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7191</t>
+          <t>7838</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -17170,12 +17170,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -17190,12 +17190,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>8029</t>
+          <t>7958</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>19598</t>
+          <t>19212</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -17205,12 +17205,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -17231,12 +17231,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>563</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6389</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -17251,7 +17251,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -17271,7 +17271,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4376</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -17286,7 +17286,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -17301,12 +17301,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8031</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -17342,12 +17342,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>626</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>6183</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -17357,12 +17357,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4154</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -17397,7 +17397,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>6999</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -17432,7 +17432,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -17453,12 +17453,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2848</t>
+          <t>2738</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11818</t>
+          <t>11953</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -17468,12 +17468,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -17488,12 +17488,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>748</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>8025</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -17508,7 +17508,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -17523,12 +17523,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>15696</t>
+          <t>15125</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -17538,12 +17538,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -17564,12 +17564,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13469</t>
+          <t>12968</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>27564</t>
+          <t>27008</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -17579,12 +17579,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10606</t>
+          <t>10537</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>22685</t>
+          <t>23119</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -17614,12 +17614,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -17634,12 +17634,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>27191</t>
+          <t>26132</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>44931</t>
+          <t>44811</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -17649,12 +17649,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -17675,12 +17675,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>95660</t>
+          <t>97364</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>113600</t>
+          <t>113902</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -17690,12 +17690,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -17710,12 +17710,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>102862</t>
+          <t>103079</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>117438</t>
+          <t>118012</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -17725,12 +17725,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17745,12 +17745,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>204689</t>
+          <t>204043</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>227238</t>
+          <t>227894</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17760,12 +17760,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,8%</t>
         </is>
       </c>
     </row>
@@ -18241,7 +18241,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6775</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -18256,7 +18256,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -18276,7 +18276,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4519</t>
+          <t>4427</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -18291,7 +18291,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -18311,7 +18311,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>7247</t>
+          <t>7527</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -18326,7 +18326,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -18791,12 +18791,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>7722</t>
+          <t>7479</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -18806,12 +18806,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -18826,12 +18826,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1974</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>8628</t>
+          <t>8772</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -18841,12 +18841,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -18861,12 +18861,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>4473</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>14029</t>
+          <t>13542</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -18876,12 +18876,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -18907,7 +18907,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3434</t>
+          <t>3862</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -18922,7 +18922,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -18977,7 +18977,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>4170</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -18992,7 +18992,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -19048,12 +19048,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>626</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>5581</t>
+          <t>5567</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -19063,12 +19063,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -19088,7 +19088,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -19103,7 +19103,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -19124,12 +19124,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>2436</t>
+          <t>2232</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>10575</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -19139,12 +19139,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -19164,7 +19164,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3143</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -19179,7 +19179,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -19194,12 +19194,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>11197</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -19209,12 +19209,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -19235,12 +19235,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2197</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>9915</t>
+          <t>9536</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -19250,12 +19250,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -19270,12 +19270,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>12155</t>
+          <t>12422</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -19285,12 +19285,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -19305,12 +19305,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>7608</t>
+          <t>7368</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>18862</t>
+          <t>17912</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -19320,12 +19320,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>15,66%</t>
         </is>
       </c>
     </row>
@@ -19346,12 +19346,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>34405</t>
+          <t>33371</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>46103</t>
+          <t>45539</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -19361,12 +19361,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -19381,12 +19381,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>37612</t>
+          <t>37567</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>48219</t>
+          <t>48253</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -19396,12 +19396,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -19416,12 +19416,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>74790</t>
+          <t>73849</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>90272</t>
+          <t>90565</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -19431,12 +19431,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,19%</t>
         </is>
       </c>
     </row>
@@ -19912,7 +19912,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>9531</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -19927,7 +19927,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>5023</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -19962,7 +19962,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -19977,12 +19977,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>885</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>8238</t>
+          <t>10980</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -19992,12 +19992,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -20023,7 +20023,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -20038,7 +20038,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -20093,7 +20093,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>2823</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -20356,7 +20356,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -20371,7 +20371,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -20426,7 +20426,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -20441,7 +20441,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -20462,12 +20462,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>7979</t>
+          <t>8116</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>19775</t>
+          <t>19800</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -20477,12 +20477,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -20497,12 +20497,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>4468</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>13904</t>
+          <t>13961</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -20512,12 +20512,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -20532,12 +20532,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>15396</t>
+          <t>15057</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>29665</t>
+          <t>30078</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -20547,12 +20547,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -20573,12 +20573,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>778</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>7254</t>
+          <t>7481</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -20588,12 +20588,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -20628,7 +20628,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -20648,7 +20648,7 @@
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>8759</t>
+          <t>8678</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -20663,7 +20663,7 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -20684,12 +20684,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>621</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>5972</t>
+          <t>6049</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -20704,7 +20704,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -20719,12 +20719,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>836</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7152</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -20734,12 +20734,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -20754,12 +20754,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>2978</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>11272</t>
+          <t>11143</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -20769,12 +20769,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -20795,12 +20795,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>7757</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>20244</t>
+          <t>19681</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -20810,12 +20810,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -20830,12 +20830,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>8256</t>
+          <t>8440</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -20845,12 +20845,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -20865,12 +20865,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>10764</t>
+          <t>10515</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>25378</t>
+          <t>25066</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -20880,12 +20880,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -20906,12 +20906,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>18231</t>
+          <t>18831</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>34018</t>
+          <t>34384</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -20921,12 +20921,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -20941,12 +20941,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>18350</t>
+          <t>17647</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>33386</t>
+          <t>34116</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -20956,12 +20956,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -20976,12 +20976,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>40413</t>
+          <t>41207</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>62834</t>
+          <t>63630</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -20991,12 +20991,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -21017,12 +21017,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>142031</t>
+          <t>142223</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>163061</t>
+          <t>163865</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -21032,12 +21032,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -21052,12 +21052,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>154862</t>
+          <t>153565</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>172526</t>
+          <t>173392</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -21067,12 +21067,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -21087,12 +21087,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>301798</t>
+          <t>301996</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>330957</t>
+          <t>330808</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -21102,12 +21102,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,85%</t>
         </is>
       </c>
     </row>
@@ -22369,7 +22369,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2773</t>
+          <t>2750</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -22384,7 +22384,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -22439,7 +22439,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3614</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -22454,7 +22454,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -22480,7 +22480,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2991</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -22495,7 +22495,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -22550,7 +22550,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>3717</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -22565,7 +22565,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>28,79%</t>
         </is>
       </c>
     </row>
@@ -22843,12 +22843,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>561</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4974</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -22858,12 +22858,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -22878,12 +22878,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>595</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5738</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -22893,12 +22893,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>45,78%</t>
         </is>
       </c>
     </row>
@@ -22919,7 +22919,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -22934,7 +22934,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -22954,12 +22954,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -22969,12 +22969,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -22989,12 +22989,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6072</t>
+          <t>5410</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11469</t>
+          <t>11378</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -23004,12 +23004,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,13%</t>
         </is>
       </c>
     </row>
@@ -23707,7 +23707,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3380</t>
+          <t>3879</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -23722,7 +23722,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -23777,7 +23777,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4007</t>
+          <t>3980</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -23792,7 +23792,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -23964,7 +23964,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2656</t>
+          <t>3191</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -23979,7 +23979,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -24014,7 +24014,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -24035,12 +24035,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6255</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>18145</t>
+          <t>17164</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -24050,12 +24050,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -24070,12 +24070,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2292</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>11433</t>
+          <t>11342</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -24085,12 +24085,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -24105,12 +24105,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>10141</t>
+          <t>10275</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>24322</t>
+          <t>24312</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -24120,7 +24120,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -24151,7 +24151,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5046</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -24166,7 +24166,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -24186,7 +24186,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>6116</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -24216,12 +24216,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>955</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -24231,12 +24231,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -24262,7 +24262,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5095</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -24277,44 +24277,44 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
+          <t>4,13%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>6379</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
           <t>4,06%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>1234</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>4723</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>4</t>
@@ -24327,12 +24327,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>714</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8198</t>
+          <t>6860</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -24342,12 +24342,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -24368,12 +24368,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11036</t>
+          <t>10363</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -24383,12 +24383,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -24408,7 +24408,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -24423,7 +24423,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -24438,12 +24438,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>3538</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>13424</t>
+          <t>13448</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -24453,12 +24453,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -24479,12 +24479,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7964</t>
+          <t>7702</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>19224</t>
+          <t>19096</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -24494,12 +24494,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -24514,12 +24514,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>9703</t>
+          <t>9456</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>24766</t>
+          <t>25169</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -24529,12 +24529,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -24549,12 +24549,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>20208</t>
+          <t>20054</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>39599</t>
+          <t>38510</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -24590,12 +24590,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>82871</t>
+          <t>83795</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>100073</t>
+          <t>100971</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -24605,12 +24605,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -24625,12 +24625,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>119849</t>
+          <t>120234</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>138958</t>
+          <t>138844</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -24640,12 +24640,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -24660,12 +24660,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>210632</t>
+          <t>210041</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>237233</t>
+          <t>236302</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -24675,12 +24675,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,69%</t>
         </is>
       </c>
     </row>
@@ -25267,7 +25267,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2358</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -25282,7 +25282,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -25337,7 +25337,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2328</t>
+          <t>2440</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -25352,7 +25352,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -25706,12 +25706,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>9155</t>
+          <t>9400</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -25721,12 +25721,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -25741,12 +25741,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>10826</t>
+          <t>11644</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -25756,12 +25756,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -25776,12 +25776,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>5940</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>17623</t>
+          <t>17598</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -25791,12 +25791,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -25822,7 +25822,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -25837,7 +25837,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -25857,7 +25857,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3717</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -25872,7 +25872,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -25887,12 +25887,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>418</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>5489</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -25907,7 +25907,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -26039,12 +26039,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>8390</t>
+          <t>8189</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -26054,12 +26054,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -26074,12 +26074,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>8208</t>
+          <t>8897</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -26089,12 +26089,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -26109,12 +26109,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>4179</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>12935</t>
+          <t>13331</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -26124,12 +26124,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -26150,12 +26150,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>6656</t>
+          <t>6591</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -26165,12 +26165,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -26185,12 +26185,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>4794</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>14913</t>
+          <t>15821</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -26200,12 +26200,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -26220,12 +26220,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>7439</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>19481</t>
+          <t>20016</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -26235,12 +26235,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -26261,12 +26261,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>39011</t>
+          <t>38693</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>49332</t>
+          <t>49423</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -26276,12 +26276,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -26296,12 +26296,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>43927</t>
+          <t>43707</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>57433</t>
+          <t>57299</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -26311,12 +26311,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -26331,12 +26331,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>86124</t>
+          <t>85611</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>103898</t>
+          <t>104050</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -26346,12 +26346,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,41%</t>
         </is>
       </c>
     </row>
@@ -26938,7 +26938,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -26953,7 +26953,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -27008,7 +27008,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>2553</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -27023,7 +27023,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -27049,7 +27049,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -27064,7 +27064,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -27119,7 +27119,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -27134,7 +27134,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -27306,7 +27306,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>3277</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -27321,7 +27321,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -27341,7 +27341,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>2414</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -27356,7 +27356,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -27377,12 +27377,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>9982</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>25272</t>
+          <t>23937</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -27392,12 +27392,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -27412,12 +27412,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>6443</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>18608</t>
+          <t>18679</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -27427,12 +27427,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -27447,12 +27447,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>20183</t>
+          <t>19076</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>38408</t>
+          <t>37812</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -27462,12 +27462,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -27488,12 +27488,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>6879</t>
+          <t>7163</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -27503,12 +27503,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -27523,12 +27523,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>755</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>8826</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -27538,12 +27538,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -27558,12 +27558,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>11752</t>
+          <t>11297</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -27573,12 +27573,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -27604,7 +27604,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>4607</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -27619,7 +27619,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -27639,7 +27639,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -27654,7 +27654,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -27669,12 +27669,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>744</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>7115</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -27684,12 +27684,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -27710,12 +27710,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>5139</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>15681</t>
+          <t>15708</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -27725,12 +27725,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -27745,12 +27745,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2258</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>10563</t>
+          <t>9934</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -27760,12 +27760,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -27780,12 +27780,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>9328</t>
+          <t>9461</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>22785</t>
+          <t>22703</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -27795,12 +27795,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -27821,12 +27821,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>9867</t>
+          <t>9934</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>22930</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -27836,12 +27836,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -27856,12 +27856,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>19358</t>
+          <t>18287</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>38308</t>
+          <t>38059</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -27871,12 +27871,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -27891,12 +27891,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>33229</t>
+          <t>33257</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>56275</t>
+          <t>55635</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -27906,12 +27906,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -27932,12 +27932,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>131285</t>
+          <t>131143</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>151220</t>
+          <t>151357</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -27947,12 +27947,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -27967,12 +27967,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>173590</t>
+          <t>173499</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>197663</t>
+          <t>197886</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -27982,12 +27982,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -28002,12 +28002,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>311417</t>
+          <t>311207</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>342013</t>
+          <t>344436</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -28017,12 +28017,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>81,11%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ19A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ19A-Estudios-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,46</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,82</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,54</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,38</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,48</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,48</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,42</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2,02</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2,06</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1,66</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1,49</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,7</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.461335264954354</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.81579460435116</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.542912853993391</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1.37890831496893</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>2.479194670767467</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>1.48305425823356</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>1.421466505313953</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>2.023724830462985</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>2.058631282007775</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>1.662335877804645</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>1.487710435132368</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>1.696846876587353</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>1,12; 2,32</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1,46; 2,39</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1,16; 2,38</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1,09; 1,77</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1,93; 3,45</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,25; 2,01</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,11; 1,86</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 3,74</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1,66; 2,75</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1,43; 2,09</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1,23; 1,97</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>1,24; 2,65</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>1.124604989119278</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1.458530260271611</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1.160856117909796</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>1.087587068958367</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>1.928806033651822</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>1.245976206631883</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>1.114102224060904</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>1.656592779463695</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>1.431881447576489</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>1.226358175358428</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>1.2409975515917</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.315435194569885</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2.394717665199857</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>2.38319024665982</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>1.771752337297528</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>3.452440241322346</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>2.007972921876525</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>1.863805938122643</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>3.743011694335881</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>2.751829386954856</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>2.089122842172197</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>1.971255732577622</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>2.649952130695253</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,84</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,6</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,34</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,87</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,77</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,75</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1,77</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1,85</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1,69</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1,56</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,57</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>1,62; 2,1</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1,45; 1,8</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1,24; 1,52</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1,26; 1,61</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,67; 2,14</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,59; 2,04</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,56; 2,02</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1,54; 2,06</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1,7; 2,02</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1,56; 1,85</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1,44; 1,69</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,42; 1,74</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.839939845006276</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.597789235958726</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.342386884135311</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1.400505356496546</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>1.867728227754701</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>1.771422369797664</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>1.754056173542546</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>1.771214237008297</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>1.853504769325343</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>1.686161767169547</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>1.556025674595219</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>1.573249605526419</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,76</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2,22</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,79</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,73</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,06</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,92</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,91</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1,72</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1,92</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2,07</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1,85</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,73</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1.624191493316638</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>1.445283547745958</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1.237141935936264</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>1.256018289611836</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>1.670516302763915</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>1.585227056412205</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>1.555214322731201</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>1.543458506165352</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>1.699687516395732</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>1.558684236003587</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>1.439779097423386</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>1.419453410481006</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>1,42; 2,31</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1,76; 3,04</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1,46; 2,42</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1,47; 2,1</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1,62; 3,08</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,56; 2,46</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>1,53; 2,94</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1,44; 2,17</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>1,62; 2,65</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>1,76; 2,54</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1,55; 2,32</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>1,52; 2,01</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2.104474179285578</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.796099672220915</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.51526594462593</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1.606617258609167</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>2.135573033831479</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>2.041389827926356</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>2.019661987607162</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>2.062145822674534</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>2.023801977479573</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>1.851813533526709</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>1.692091783189445</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>1.743169875667071</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,137 +923,269 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,79</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,78</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,48</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,99</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,78</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,78</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1,76</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1,89</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1,78</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1,63</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,62</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>1.759960822840661</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2.217657506937006</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.788650974039771</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.734345422327547</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>2.061905665914611</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>1.924040091339545</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>1.913359019164256</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>1.722242903804446</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>1.924287524450056</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>2.068184111581365</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>1.849562678192348</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>1.728686415728157</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>1,6; 2,0</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1,61; 2,03</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1,36; 1,69</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1,37; 1,68</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,8; 2,26</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1,62; 1,99</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,61; 2,06</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1,59; 2,0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1,75; 2,05</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>1,66; 1,94</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1,52; 1,79</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,51; 1,76</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1.420860552898651</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>1.757556991583611</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>1.456131144431314</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>1.474243245560436</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>1.622074834444462</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>1.561649308471047</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>1.529185995108556</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>1.437814281175945</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>1.623959712558259</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>1.763393973786227</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>1.553835278134326</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>1.520496879905964</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2.305261192763719</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.037016841117277</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.421420021552648</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>2.102857891559669</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>3.078703550695952</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>2.462674736402588</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>2.944582420579606</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>2.166785392993922</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>2.652918355999734</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>2.542654480465874</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>2.316760465769824</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>2.007445496217165</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1.786825818666424</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1.782453159258854</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.48086844616021</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1.502659336363387</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>1.993241561919901</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>1.777420584992033</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>1.779456636127368</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>1.764156338362921</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>1.892420671133467</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>1.779921737372992</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>1.632278737270179</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>1.624855584934637</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>1.596937231107316</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>1.609879991487878</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>1.357537641162079</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>1.367164256115675</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>1.801622482204842</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>1.623542336790238</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>1.611469245960365</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>1.587362794801572</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>1.752395683607792</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>1.664851541796112</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>1.519608054587339</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>1.505309389254132</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.001312892169774</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.030666812008528</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.686592356787395</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.68380003308149</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>2.263751846685783</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>1.990088529381051</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>2.062265646559934</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>2.002802040345152</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>2.046604950324058</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>1.935848419508594</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>1.790761545174466</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>1.761780115122304</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1204,14 +1193,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
